--- a/drg/menaka dd/excel for calculation/stair dead load calculation.xlsx
+++ b/drg/menaka dd/excel for calculation/stair dead load calculation.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89181E3-7125-4451-9DBF-E76457D73B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WL(resting on beam and slab)" sheetId="1" r:id="rId1"/>
@@ -16,7 +17,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">Sheet1!$A$1:$L$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'WL(resting on beam and slab)'!$A$1:$P$82</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -346,36 +347,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="28">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="#,##0&quot;''&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0&quot;''&quot;"/>
-    <numFmt numFmtId="168" formatCode="#0.00#&quot;m&quot;"/>
-    <numFmt numFmtId="169" formatCode="0.000#&quot;m&quot;"/>
-    <numFmt numFmtId="170" formatCode="0.000&quot;m&quot;"/>
-    <numFmt numFmtId="171" formatCode="#,##0&quot;'&quot;"/>
-    <numFmt numFmtId="172" formatCode="0%&quot; opening&quot;"/>
-    <numFmt numFmtId="173" formatCode="#,##0&quot;'' wall  (KN/m)&quot;"/>
-    <numFmt numFmtId="174" formatCode="#,##0.0&quot;'' wall  (KN/m)&quot;"/>
-    <numFmt numFmtId="175" formatCode="&quot; WL (with&quot;\ 0%\ &quot;opening)&quot;\ &quot;Unit: KN&quot;"/>
-    <numFmt numFmtId="176" formatCode="\ 0%"/>
-    <numFmt numFmtId="177" formatCode="&quot;=&quot;0.00#"/>
-    <numFmt numFmtId="178" formatCode="#&quot;mm&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.00#&quot;mm&quot;"/>
-    <numFmt numFmtId="180" formatCode="0.0000"/>
-    <numFmt numFmtId="181" formatCode="0.000#&quot; m&quot;"/>
-    <numFmt numFmtId="182" formatCode="&quot; wall area with&quot;\ 0%\ &quot;opening=&quot;"/>
-    <numFmt numFmtId="183" formatCode="#&quot; Ltr.&quot;"/>
-    <numFmt numFmtId="184" formatCode="0.00#&quot; m²&quot;"/>
-    <numFmt numFmtId="185" formatCode="0.0#&quot; KN/m²&quot;"/>
-    <numFmt numFmtId="186" formatCode="0.00#&quot; KN/m²&quot;"/>
-    <numFmt numFmtId="187" formatCode="0.0#&quot;KN/m³&quot;"/>
-    <numFmt numFmtId="188" formatCode="#\ &quot;KN/m³&quot;"/>
-    <numFmt numFmtId="189" formatCode="0.00#\ &quot;KN/m³&quot;"/>
-    <numFmt numFmtId="190" formatCode="0#&quot; KN/m³&quot;"/>
-    <numFmt numFmtId="191" formatCode="0.0#&quot; KN/m³&quot;"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;''&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0&quot;''&quot;"/>
+    <numFmt numFmtId="167" formatCode="#0.00#&quot;m&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.000#&quot;m&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.000&quot;m&quot;"/>
+    <numFmt numFmtId="170" formatCode="#,##0&quot;'&quot;"/>
+    <numFmt numFmtId="171" formatCode="0%&quot; opening&quot;"/>
+    <numFmt numFmtId="172" formatCode="#,##0&quot;'' wall  (KN/m)&quot;"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0&quot;'' wall  (KN/m)&quot;"/>
+    <numFmt numFmtId="174" formatCode="&quot; WL (with&quot;\ 0%\ &quot;opening)&quot;\ &quot;Unit: KN&quot;"/>
+    <numFmt numFmtId="175" formatCode="\ 0%"/>
+    <numFmt numFmtId="176" formatCode="&quot;=&quot;0.00#"/>
+    <numFmt numFmtId="177" formatCode="#&quot;mm&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.00#&quot;mm&quot;"/>
+    <numFmt numFmtId="179" formatCode="0.0000"/>
+    <numFmt numFmtId="180" formatCode="0.000#&quot; m&quot;"/>
+    <numFmt numFmtId="181" formatCode="&quot; wall area with&quot;\ 0%\ &quot;opening=&quot;"/>
+    <numFmt numFmtId="182" formatCode="#&quot; Ltr.&quot;"/>
+    <numFmt numFmtId="183" formatCode="0.00#&quot; m²&quot;"/>
+    <numFmt numFmtId="184" formatCode="0.0#&quot; KN/m²&quot;"/>
+    <numFmt numFmtId="185" formatCode="0.00#&quot; KN/m²&quot;"/>
+    <numFmt numFmtId="186" formatCode="0.0#&quot;KN/m³&quot;"/>
+    <numFmt numFmtId="187" formatCode="#\ &quot;KN/m³&quot;"/>
+    <numFmt numFmtId="188" formatCode="0.00#\ &quot;KN/m³&quot;"/>
+    <numFmt numFmtId="189" formatCode="0#&quot; KN/m³&quot;"/>
+    <numFmt numFmtId="190" formatCode="0.0#&quot; KN/m³&quot;"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -594,13 +595,13 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -609,34 +610,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="183" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="186" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="191" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -656,11 +657,15 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -668,243 +673,239 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="175" fontId="3" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="180" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="centerContinuous" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="centerContinuous" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="182" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="185" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="181" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="186" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="186" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="187" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="centerContinuous" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="centerContinuous" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="188" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -992,10 +993,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:rad>
                       <m:radPr>
                         <m:degHide m:val="on"/>
@@ -1242,10 +1240,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1370,10 +1365,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1506,7 +1498,7 @@
                   <m:f>
                     <m:fPr>
                       <m:ctrlPr>
-                        <a:rPr lang="en-US" sz="1400" i="1">
+                        <a:rPr lang="en-US" sz="1400" b="0" i="1">
                           <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         </a:rPr>
                       </m:ctrlPr>
@@ -1521,7 +1513,7 @@
                       <m:f>
                         <m:fPr>
                           <m:ctrlPr>
-                            <a:rPr lang="en-US" sz="1400" i="1">
+                            <a:rPr lang="en-US" sz="1400" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                           </m:ctrlPr>
@@ -1577,7 +1569,7 @@
                         <a:rPr lang="en-US" sz="1400" b="0" i="1">
                           <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         </a:rPr>
-                        <m:t>𝑤𝑖𝑑𝑡h</m:t>
+                        <m:t>𝑤𝑖𝑑𝑡ℎ</m:t>
                       </m:r>
                       <m:r>
                         <a:rPr lang="en-US" sz="1400" b="0" i="1">
@@ -1694,7 +1686,7 @@
                         <a:rPr lang="en-US" sz="1400" b="0" i="1">
                           <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         </a:rPr>
-                        <m:t>𝑤𝑖𝑑𝑡h</m:t>
+                        <m:t>𝑤𝑖𝑑𝑡ℎ</m:t>
                       </m:r>
                       <m:r>
                         <a:rPr lang="en-US" sz="1400" b="0" i="1">
@@ -2229,10 +2221,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2363,10 +2352,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2491,10 +2477,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:rad>
                       <m:radPr>
                         <m:degHide m:val="on"/>
@@ -2680,10 +2663,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2694,7 +2674,7 @@
                       <a:rPr lang="en-US" sz="1100" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
-                      <m:t>𝑖𝑑𝑡h</m:t>
+                      <m:t>𝑖𝑑𝑡ℎ</m:t>
                     </m:r>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" b="0" i="1">
@@ -2713,10 +2693,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2740,10 +2717,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -3116,9 +3090,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3156,9 +3130,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3193,7 +3167,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3228,7 +3202,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3401,32 +3375,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L62"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" style="20" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="20" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" style="20" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="20" customWidth="1"/>
     <col min="3" max="3" width="17" style="20" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" style="20" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" style="20" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.44140625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="20" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" style="20" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.42578125" style="20" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" style="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" style="20" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" style="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" style="20"/>
-    <col min="13" max="13" width="21.6640625" style="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.6640625" style="20"/>
+    <col min="10" max="10" width="7.7109375" style="20" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" style="20"/>
+    <col min="13" max="13" width="21.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.7109375" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="13.9" x14ac:dyDescent="0.25">
       <c r="G2" s="21" t="s">
         <v>51</v>
       </c>
@@ -3435,7 +3409,7 @@
       </c>
       <c r="I2" s="22"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="5" t="s">
         <v>37</v>
@@ -3454,7 +3428,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="5" t="s">
         <v>38</v>
@@ -3473,7 +3447,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B5" s="23" t="s">
         <v>44</v>
       </c>
@@ -3491,7 +3465,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B6" s="23" t="s">
         <v>45</v>
       </c>
@@ -3509,7 +3483,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B7" s="23" t="s">
         <v>46</v>
       </c>
@@ -3527,7 +3501,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
         <v>39</v>
@@ -3537,7 +3511,7 @@
         <v>2.744-0.356</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
         <v>53</v>
@@ -3547,7 +3521,7 @@
         <v>2.3879999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="5" t="s">
         <v>47</v>
@@ -3557,7 +3531,7 @@
         <v>2.744-0.127</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
         <v>53</v>
@@ -3567,7 +3541,7 @@
         <v>2.617</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
         <v>40</v>
@@ -3579,7 +3553,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B13" s="23" t="s">
         <v>41</v>
       </c>
@@ -3587,7 +3561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="14.45" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="32"/>
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
@@ -3609,7 +3583,7 @@
       <c r="G15" s="35"/>
       <c r="H15" s="36"/>
     </row>
-    <row r="16" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="14.45" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="67" t="s">
         <v>54</v>
       </c>
@@ -3626,7 +3600,7 @@
       </c>
       <c r="H16" s="37"/>
     </row>
-    <row r="17" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="14.45" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="73"/>
       <c r="B17" s="74">
         <f>+H3</f>
@@ -3649,7 +3623,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A18" s="77" t="s">
         <v>34</v>
       </c>
@@ -3674,7 +3648,7 @@
         <v>=1*0.115*19.2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="14.45" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="81"/>
       <c r="B19" s="82">
         <f>ROUND((C3*C9*C12),2)</f>
@@ -3697,7 +3671,7 @@
         <v>2.2080000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A20" s="77" t="s">
         <v>35</v>
       </c>
@@ -3719,7 +3693,7 @@
       </c>
       <c r="F20" s="85"/>
     </row>
-    <row r="21" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="14.45" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="81"/>
       <c r="B21" s="82">
         <f>ROUND((C3*C11*C12),2)</f>
@@ -3739,28 +3713,28 @@
       </c>
       <c r="F21" s="86"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A22" s="38"/>
       <c r="B22" s="32"/>
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
       <c r="E22" s="32"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A23" s="38"/>
       <c r="B23" s="32"/>
       <c r="C23" s="32"/>
       <c r="D23" s="32"/>
       <c r="E23" s="32"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A24" s="38"/>
       <c r="B24" s="32"/>
       <c r="C24" s="32"/>
       <c r="D24" s="32"/>
       <c r="E24" s="32"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>60</v>
       </c>
@@ -3769,12 +3743,12 @@
       <c r="D25" s="40"/>
       <c r="E25" s="32"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B28" s="23" t="s">
         <v>61</v>
       </c>
@@ -3782,7 +3756,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="5" t="s">
         <v>63</v>
@@ -3794,7 +3768,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="5" t="s">
         <v>74</v>
@@ -3806,7 +3780,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B31" s="23" t="s">
         <v>62</v>
       </c>
@@ -3814,7 +3788,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B32" s="23" t="s">
         <v>65</v>
       </c>
@@ -3822,7 +3796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="16.899999999999999" x14ac:dyDescent="0.25">
       <c r="B33" s="23" t="s">
         <v>66</v>
       </c>
@@ -3830,13 +3804,13 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B34" s="43" t="s">
         <v>70</v>
       </c>
       <c r="C34" s="38"/>
     </row>
-    <row r="35" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="23" t="s">
         <v>68</v>
       </c>
@@ -3847,7 +3821,7 @@
       <c r="K35" s="44"/>
       <c r="L35" s="44"/>
     </row>
-    <row r="36" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="23" t="s">
         <v>53</v>
       </c>
@@ -3858,7 +3832,7 @@
       <c r="K36" s="44"/>
       <c r="L36" s="44"/>
     </row>
-    <row r="37" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="23" t="s">
         <v>76</v>
       </c>
@@ -3869,7 +3843,7 @@
       <c r="K37" s="44"/>
       <c r="L37" s="44"/>
     </row>
-    <row r="38" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="23" t="s">
         <v>53</v>
       </c>
@@ -3880,7 +3854,7 @@
       <c r="K38" s="44"/>
       <c r="L38" s="44"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B39" s="23" t="s">
         <v>69</v>
       </c>
@@ -3890,7 +3864,7 @@
       </c>
       <c r="K39" s="32"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B40" s="23" t="s">
         <v>53</v>
       </c>
@@ -3900,7 +3874,7 @@
       </c>
       <c r="K40" s="32"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B41" s="43" t="s">
         <v>71</v>
       </c>
@@ -3910,12 +3884,12 @@
       </c>
       <c r="K41" s="32"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A42" s="48"/>
       <c r="C42" s="32"/>
       <c r="E42" s="49"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A43" s="50" t="s">
         <v>81</v>
       </c>
@@ -3930,7 +3904,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B44" s="23" t="s">
         <v>82</v>
       </c>
@@ -3945,7 +3919,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A45" s="38"/>
       <c r="B45" s="23" t="s">
         <v>83</v>
@@ -3963,7 +3937,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A46" s="38"/>
       <c r="B46" s="5" t="s">
         <v>84</v>
@@ -3977,7 +3951,7 @@
       <c r="G46" s="56"/>
       <c r="H46" s="57"/>
     </row>
-    <row r="47" spans="1:12" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="16.899999999999999" x14ac:dyDescent="0.25">
       <c r="A47" s="38"/>
       <c r="B47" s="5" t="s">
         <v>53</v>
@@ -3991,7 +3965,7 @@
       <c r="G47" s="56"/>
       <c r="H47" s="57"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B48" s="23" t="s">
         <v>89</v>
       </c>
@@ -4066,7 +4040,7 @@
       </c>
       <c r="C54" s="53">
         <f>ROUNDUP(((G54*12)+H54)*0.0254,3)</f>
-        <v>0.17799999999999999</v>
+        <v>0.153</v>
       </c>
       <c r="D54" s="32"/>
       <c r="E54" s="32"/>
@@ -4074,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="H54" s="30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -4102,15 +4076,15 @@
       </c>
       <c r="C56" s="53">
         <f>ROUNDUP(((G56*12)+H56)*0.0254,3)</f>
-        <v>1.0669999999999999</v>
+        <v>1.22</v>
       </c>
       <c r="D56" s="32"/>
       <c r="E56" s="32"/>
       <c r="G56" s="29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H56" s="55">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -4127,7 +4101,7 @@
       <c r="E57" s="94"/>
       <c r="F57" s="4"/>
     </row>
-    <row r="58" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
       <c r="B58" s="97" t="s">
         <v>96</v>
@@ -4144,7 +4118,7 @@
       </c>
       <c r="C59" s="4" t="str">
         <f>CONCATENATE("(",C54,"*",C55,"*",C57,")/{2*sqrt(",C54,"^2+",C55,"^2}")</f>
-        <v>(0.178*0.254*25)/{2*sqrt(0.178^2+0.254^2}</v>
+        <v>(0.153*0.254*25)/{2*sqrt(0.153^2+0.254^2}</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -4157,7 +4131,7 @@
       </c>
       <c r="C60" s="17">
         <f>(0.5*C54*C55*C57)/(SQRT(C54^2+C55^2))</f>
-        <v>1.8221167310292938</v>
+        <v>1.6382454557113664</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -4178,20 +4152,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="4" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="4"/>
+    <col min="2" max="2" width="26.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>80</v>
       </c>
@@ -4202,7 +4176,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>82</v>
       </c>
@@ -4217,7 +4191,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>83</v>
       </c>
@@ -4232,7 +4206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>77</v>
       </c>
@@ -4247,7 +4221,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>78</v>
       </c>
@@ -4262,7 +4236,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>79</v>
       </c>
@@ -4284,7 +4258,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>85</v>
       </c>
@@ -4301,7 +4275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>84</v>
       </c>
@@ -4322,7 +4296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>53</v>
       </c>
@@ -4346,7 +4320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>86</v>
       </c>
@@ -4355,7 +4329,7 @@
         <v>0.115*3.607</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>53</v>
       </c>
@@ -4364,7 +4338,7 @@
         <v>0.41480499999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B12" s="15">
         <v>0.2</v>
       </c>
@@ -4373,7 +4347,7 @@
         <v>0.8*0.415</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>53</v>
       </c>
@@ -4382,7 +4356,7 @@
         <v>0.33184400000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>87</v>
       </c>
@@ -4391,7 +4365,7 @@
         <v>(0.415*1.004*19.2)/14.925</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>53</v>
       </c>
@@ -4400,7 +4374,7 @@
         <v>0.53575751180965991</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="13.9" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>88</v>
       </c>
@@ -4409,7 +4383,7 @@
         <v>(0.332*1.004*19.2)/14.925</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="25.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" ht="25.15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5" t="s">
         <v>53</v>
       </c>
@@ -4426,15 +4400,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" style="1"/>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="99" t="s">
         <v>5</v>
       </c>
@@ -4444,17 +4418,17 @@
       <c r="E1" s="99"/>
       <c r="F1" s="99"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -4465,7 +4439,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4482,7 +4456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -4493,7 +4467,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4505,12 +4479,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -4521,7 +4495,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -4535,7 +4509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -4549,7 +4523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -4561,7 +4535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -4582,7 +4556,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -4593,7 +4567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -4615,7 +4589,7 @@
         <v>3.8862000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -4634,12 +4608,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -4650,7 +4624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -4662,7 +4636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -4674,7 +4648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -4692,7 +4666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -4700,7 +4674,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -4729,14 +4703,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -4744,7 +4718,7 @@
         <v>11.48</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -4753,7 +4727,7 @@
         <v>4.5920000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3">
         <f>B2*1000</f>
         <v>45.92</v>
@@ -4763,7 +4737,7 @@
         <v>9.4999999999999973E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D4">
         <f>D3/0.701</f>
         <v>0.13552068473609127</v>
